--- a/artfynd/A 39318-2022 artfynd.xlsx
+++ b/artfynd/A 39318-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121075262</v>
+        <v>121072304</v>
       </c>
       <c r="B2" t="n">
-        <v>57752</v>
+        <v>57755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,10 +708,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694576</v>
+        <v>694590</v>
       </c>
       <c r="R2" t="n">
-        <v>6628721</v>
+        <v>6628739</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +759,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Calluna AB, JPN0075</t>
+          <t>Calluna AB JPN0075</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072304</v>
+        <v>121075262</v>
       </c>
       <c r="B3" t="n">
-        <v>57752</v>
+        <v>57755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,14 +839,10 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694590</v>
+        <v>694576</v>
       </c>
       <c r="R3" t="n">
-        <v>6628739</v>
+        <v>6628721</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,27 +886,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Calluna AB JPN0075</t>
+          <t>Calluna AB, JPN0075</t>
         </is>
       </c>
       <c r="AD3" t="b">
